--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>https://careers.stanfordhealthcare.org/</t>
+          <t>https://careers.stanfordhealthcare.org/us/en/job/R2551913/Audiologist-I</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>260417-017</t>
+          <t>260417-018</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Audiologist, Clinical Specialist – Otolaryngology</t>
+          <t>Doctor of Audiology (NYEE, Full-time Days)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Clinical-Admin</t>
+          <t>Clinical</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mountsinai.org/jobs/3033433?lang=en-us</t>
+          <t>https://careers.mountsinai.org/jobs/3033391?lang=en-us</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1356,24 +1356,24 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Tier-1 NYC AMC (Icahn School of Medicine). 'Clinical Specialist' within Otolaryngology-HNS — typically senior-scope/subspecialty, teaching, cross-team consult. Adjacent to Mount Sinai's Center for Hearing &amp; Balance research programs. PSLF-eligible. Adjacent-role flag for Cece.</t>
+          <t>Tier-1 NYC AMC. Doctor of Audiology at New York Eye and Ear Infirmary — full-time days. Appears to be the replacement req for the closed 260417-007 (Mount Sinai 3024126). PSLF-eligible. Pure clinical, surfaced per Tier-1 rule.</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>jobs/260417-017.md</t>
+          <t>jobs/260417-018.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>260417-018</t>
+          <t>260417-019</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Doctor of Audiology (NYEE, Full-time Days)</t>
+          <t>Audiologist – Full Time, Days</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>NewYork-Presbyterian (Brooklyn Methodist Hospital)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Academic</t>
+          <t>Hospital-NonProfit</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Brooklyn, NY</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Not listed (NYP competitive; verify at apply page)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026 (active)</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://careers.mountsinai.org/jobs/3033391?lang=en-us</t>
+          <t>https://careers.nyp.org/job/brooklyn/audiologist-full-time-days/19715/90947179360</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Mount Sinai Careers</t>
+          <t>NYP Careers</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Tier-1 NYC AMC. Doctor of Audiology at New York Eye and Ear Infirmary — full-time days. Appears to be the replacement req for the closed 260417-007 (Mount Sinai 3024126). PSLF-eligible. Pure clinical, surfaced per Tier-1 rule.</t>
+          <t>Tier-1 NYC non-profit (NYP Brooklyn Methodist is part of NewYork-Presbyterian; teaching hospital for Columbia Vagelos &amp; Weill Cornell). Posted 2026-01-23 so likely still accepting applications. PSLF-eligible. Pure clinical (diagnostic + rehab, adult &amp; pediatric).</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>jobs/260417-018.md</t>
+          <t>jobs/260417-019.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>260417-019</t>
+          <t>260417-020</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Audiologist – Full Time, Days</t>
+          <t>Audiologist</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian (Brooklyn Methodist Hospital)</t>
+          <t>Kaiser Permanente (South San Francisco Medical Offices)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Brooklyn, NY</t>
+          <t>South San Francisco, CA</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Not listed (NYP competitive; verify at apply page)</t>
+          <t>$120,400 – $155,760 / yr</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026 (active)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1539,15 +1539,19 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>https://careers.nyp.org/job/brooklyn/audiologist-full-time-days/19715/90947179360</t>
+          <t>https://www.kaiserpermanentejobs.org/job/south-san-francisco/audiologist/641/80366214896</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>NYP Careers</t>
+          <t>Kaiser Permanente Jobs</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1557,19 +1561,19 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Tier-1 NYC non-profit (NYP Brooklyn Methodist is part of NewYork-Presbyterian; teaching hospital for Columbia Vagelos &amp; Weill Cornell). Posted 2026-01-23 so likely still accepting applications. PSLF-eligible. Pure clinical (diagnostic + rehab, adult &amp; pediatric).</t>
+          <t>Tier-1 SF Bay. Kaiser NorCal integrated non-profit — typically PSLF-eligible (verify specific Kaiser entity at apply). Full-time day shift (M–F, 8:30a–5:30p); Head &amp; Neck Audiology dept. Min 1 yr post-licensure — within Cece's range. Pure clinical but high salary band and predictable schedule.</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>jobs/260417-019.md</t>
+          <t>jobs/260417-020.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>260417-020</t>
+          <t>260417-021</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1579,92 +1583,284 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Audiology (in Otolaryngology–Head and Neck Surgery)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Columbia University (ColumbiaDoctors / Columbia University Medical Center)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Teaching</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Westchester / New York, NY</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Set based on qualifications, experience, education, and departmental budget (not published)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.snagajob.com/jobs/1091818426</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Snagajob / HEARCareers / HERC Jobs</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Tier-1 NYC academic faculty appointment (Vagelos College of Physicians &amp; Surgeons). Primary duty is diagnostic audiology at ColumbiaDoctors Westchester with occasional travel to NYC — hybrid location. Assistant Professor rank means teaching/supervision of medical students, ENT residents, and AuD student clinicians. NY State Audiologist license + NY Hearing Aid Dispensary license + ASHA CCC-A required. PSLF-eligible. Multiple cross-postings (Snagajob 1091818426, Snagajob 1109149870, HEARCareers 21003011, HERC Jobs 21003892) — HEARCareers listing flagged "no longer active" but other boards indicate the req has been re-posted / is actively hiring. Worth contacting Columbia OHNS HR directly to confirm current status before applying.</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-021.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>260417-022</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Audiologist</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Kaiser Permanente (South San Francisco Medical Offices)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Hospital-NonProfit</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Offsite Audiologist — Mount Sinai West</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Clinical</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>South San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>$120,400 – $155,760 / yr</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>2026 (active)</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kaiserpermanentejobs.org/job/south-san-francisco/audiologist/641/80366214896</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Kaiser Permanente Jobs</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.mountsinai.org/jobs/3029840?lang=en-us</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Careers</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>Tier-1 SF Bay. Kaiser NorCal integrated non-profit — typically PSLF-eligible (verify specific Kaiser entity at apply). Full-time day shift (M–F, 8:30a–5:30p); Head &amp; Neck Audiology dept. Min 1 yr post-licensure — within Cece's range. Pure clinical but high salary band and predictable schedule.</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>jobs/260417-020.md</t>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Tier-1 NYC AMC (Icahn School of Medicine). "Offsite" framing implies a community/ambulatory-site placement rather than Mount Sinai Hospital main campus — likely a satellite ENT/audiology clinic. PSLF-eligible. Couldn't retrieve full job description (WebFetch against careers.mountsinai.org returned the template page without posting body); confirmed the req is still live via Mount Sinai careers search index. Pure clinical — surfaced per Tier-1 "always include" rule.</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-022.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>260417-023</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist — Per Diem (req 132478)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>UC San Diego Health</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-Research</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Per-diem hourly (not published in search snapshot)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026 (active)</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://employment.ucsd.edu/audiologist-per-diem-132478/job/28537210</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>UCSD Health Employment</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Tier-1 San Diego academic medical center. Per-diem (flexible hours). Listing explicitly mentions "research related to hearing" alongside diagnostic / habilitative / rehabilitative services and clinical supervision of AuD students — meaningful research touchpoint for Cece within an AMC. PSLF-eligible. AuD + CA licensure expected. Pure clinical classification but research-adjacent; flagged research_flag=true. Per-diem may be a useful entry point if she wants to blend UCSD hours with other work.</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-023.md</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2818,6 +3014,114 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>260417-017</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist, Clinical Specialist – Otolaryngology</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-Admin</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026 (active)</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.mountsinai.org/jobs/3033433?lang=en-us</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Careers</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Tier-1 NYC AMC (Icahn School of Medicine). 'Clinical Specialist' within Otolaryngology-HNS — typically senior-scope/subspecialty, teaching, cross-team consult. Adjacent to Mount Sinai's Center for Hearing &amp; Balance research programs. PSLF-eligible. Adjacent-role flag for Cece.</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>jobs/closed/260417-017.md</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Posting removed — Mount Sinai careers page returns 404 "page no longer exists" for req 3033433.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2829,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,6 +3348,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Third scheduled run on 2026-04-17. Added 3 new: Columbia Assistant Professor of Audiology in Otolaryngology (NYC/Westchester, High), Mount Sinai West Offsite Audiologist (NYC, Low), UCSD Audiologist Per Diem (San Diego, Low, research-flagged). Closed 1 (Mount Sinai 3033433 — req pulled). Updated 10 existing active jobs (all re-verified live; Stanford Audiologist I apply_url updated to specific req R2551913). WebFetch against several employer ATS (Mount Sinai, MGB Workday, Kaiser, NYP) returned 404/empty but employer search indexes confirm postings remain live — held active. Excluded a Staffing Proxy remote audiologist role (TX-license gate).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -58,9 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -428,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -552,6 +559,1372 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Details File</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>260417-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Instructor or Assistant Professor — Doctor of Audiology Program</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>MGH Institute of Health Professions</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Teaching</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Charlestown / Boston, MA</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.chronicle.com/job/37887042/instructor-or-assistant-professor-audiology-program/</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Chronicle of Higher Ed / MGH IHP</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Clinical faculty position in MGH Institute AuD program; helps launch a new Audiology Graduate Certificate Program in June 2026. Stated req: 5 yrs post-graduation clinical experience — borderline for Cece's 2–3 yrs post-AuD; AuD training years plus VA/fellowship work may count toward this, worth inquiring. AuD accepted (not PhD-required). Strong non-clinical fit aligned with Cece's teaching/transition priorities.</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-001.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>260417-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Audiology (Otolaryngology Head and Neck Surgery)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Columbia University Medical Center</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-Research</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Westchester, NY (with occasional NYC travel)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.snagajob.com/jobs/1109149870</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Snagajob / Columbia Careers</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>AuD-accepted faculty role (not PhD-required) — rare. Duties include diagnostic audiology, hearing-aid management, teaching medical students / ENT residents / AuD students, AND participation in clinical research opportunities. Good hybrid clinical+teaching+research fit. Westchester counts as NYC metro per her hard-filter Tier 1.</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-002.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>260417-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Audiology Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mass General Brigham (Mass Eye and Ear)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-Admin</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>$86,611 – $126,027</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiology-manager-at-mass-general-brigham-4388529219</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Stated req: 3-5 years audiology practice + 2-3 years leadership preferred — borderline for Cece's 2-3 yrs post-AuD; AuD training years may count and her multi-VA experience includes team coordination. Mass Eye and Ear is a non-profit AMC → PSLF-eligible. Strong clinical-admin fit.</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-003.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>260417-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Staff / Sr. Audiologist</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>UCSF Health</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Clinical-Admin</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/staff-sr-audiologist-at-ucsf-health-4402603000</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / UCSF Health</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Staff level has no minimum years (just licensure); Sr. level requires 5 yrs post-licensure. Role includes supervising clinical services, mentoring externs/audiologists, helping develop new programs and policies — clinical-admin lean. UCSF = academic medical center, PSLF-eligible. Cece can apply at Staff level and note Sr. as stretch.</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-004.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>260417-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Remote AL Audiologist</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Earlens Corporation</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>$90,000 – $125,000</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-al-audiologist-at-earlens-corporation-4399972750</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Earlens</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Adjacent industry role — AuD+VA+research background transfers. Fully remote. Stated req: 2-3 yrs clinical diagnostic + hearing aid dispensing → direct match for Cece's experience level. Device company → not PSLF, but a clean exit ramp from pure in-person clinical while keeping her AuD in play.</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-005.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>260417-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Doctor of Audiology — New York Eye and Ear Infirmary</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.mountsinai.org/jobs/3033391?lang=en-us</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Careers</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Pure clinical, but Tier 1 and at a major AMC (NYEE) with a strong research / ENT ecosystem. Surfaced for Cece to decide — she may want this as a foot-in-the-door to the NYEE / Mount Sinai research infrastructure.</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-006.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>260417-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Doctor of Audiology — Pediatric Audiology, New York Eye and Ear Infirmary</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Mount Sinai Health System</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/doctor-of-audiology-pediatric-audiology-new-york-eye-and-ear-infirmary-of-mount-sinai-full-time-days-at-mount-sinai-health-system-4398168781</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Mount Sinai</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Pure clinical, pediatric. Surfaced because Tier 1 and AMC. Apply URL routes through LinkedIn.</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-007.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>260417-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>UCSF Health</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-at-ucsf-health-4402581905</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / UCSF Health</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Pure clinical (85% clinical). Separate from the Staff/Sr. posting (#260417-004). Tier 1 AMC, PSLF-eligible. AuD or equivalent accepted.</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-008.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>260417-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist — Mass Eye and Ear</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>$70,990 – $101,202</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-at-mass-general-brigham-4378038380</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Mass General Brigham</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Stated req: 1 year full-time work experience (including traineeship) — new grads welcome. Excellent fit for Cece's years. Tier 1, non-profit AMC, PSLF-eligible. Pure clinical but at a top-tier audiology service.</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-009.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>260417-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist II</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Boston Children's Hospital</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Waltham, MA</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-ii-at-boston-children-s-hospital-4371243962</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Boston Children's</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric. Boston Children's also has a Director of Audiology Research and a research coordinator program — worth keeping this employer on the radar for more research-adjacent openings. Tier 1 / PSLF-eligible.</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-010.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>260417-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric Audiologist — Flexible Hours (24-40 hrs/week)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Tufts Medicine</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/pediatric-audiologist-flexible-hours-24-40-hours-per-week-at-tufts-medicine-4382153688</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Tufts Medicine</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Flexible hours option (24-40 hrs/week) — potentially attractive if she wanted to combine this with a part-time research/teaching gig. Boston = Tier 1. Tufts is non-profit.</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-011.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>260417-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist — Audiology</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Rady Children's Hospital-San Diego</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-audiology-at-rady-children-s-hospital-san-diego-4390731063</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Rady Children's</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Pediatric. San Diego = Tier 1. Non-profit children's hospital → PSLF-eligible. Per-diem variant also posted (skipped as near-duplicate).</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-012.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>260417-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-at-kaiser-permanente-4376416354</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Kaiser is a large non-profit integrated system; Kaiser audiologists are salaried. San Diego = Tier 1. PSLF treatment of Kaiser is jurisdiction-specific — check for her plan.</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-013.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>260417-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Audiologist — Encinitas Clinic</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Scripps Health</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Hospital-NonProfit</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Encinitas, CA (San Diego metro)</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/audiologist-encinitas-clinic-at-scripps-health-4383275097</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Scripps Health</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Scripps is non-profit. Encinitas is San Diego metro (Tier 1). Pure clinical.</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-014.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>260417-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Remote Audiologist Dx (CA)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Earlens Corporation</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Remote (US)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/remote-audiologist-dx-ca-at-earlens-corporation-4395898638</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn / Earlens</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Companion posting to #260417-005 (Remote AL). Remote/industry. Different license/track (Dx). Listed separately so Cece can compare; if Earlens lets her pick, the AL role has clearer salary data.</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>jobs/260417-015.md</t>
         </is>
       </c>
     </row>
@@ -716,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -771,6 +2144,38 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>First pipeline run with job files created. Primary sources: LinkedIn metros (NYC, Boston, SF, SD, Remote), Chronicle of Higher Ed, Mount Sinai, Snagajob, Earlens. USAJobs searches timed out — retry next run. NYU Langone + Sonova + Starkey career portals did not render listings; queued for next run. No Pass B refreshes (no prior active jobs).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
